--- a/rod_hotels_ml_ready.xlsx
+++ b/rod_hotels_ml_ready.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ8"/>
+  <dimension ref="A1:BS8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,302 +441,347 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__0_page_de_connexion__sous_etape_rod__id__data__code_h__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__api_portfolio__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__n_a__commentaire_thomas_innolab__complete_par_le_user_au_moment_de_la_connexion</t>
+          <t>etape_rod__0_page_de_connexion__sous_etape_rod__id__data__code_h</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__0_page_de_connexion__sous_etape_rod__id__data__nom_de_l_hotel__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__api_portfolio__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__non__data_exploitee_dans_la_simulation_actuellement__n_a__commentaire_thomas_innolab__remonte_automatiquement</t>
+          <t>etape_rod__0_page_de_connexion__sous_etape_rod__id__data__nom_de_l_hotel</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__adresse_postale_1__deja_dans_rod_au_moment_ou_le_user_se_connecte__n_a__accor_api_portfolio__api_portfolio__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__n_a__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_d_un_concept_de_corner_de_vente</t>
+          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__adresse_postale_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__adresse_postale_2__deja_dans_rod_au_moment_ou_le_user_se_connecte__n_a__accor_api_portfolio__api_portfolio__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__n_a__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_d_un_concept_de_corner_de_vente</t>
+          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__adresse_postale_2</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__code_postal__deja_dans_rod_au_moment_ou_le_user_se_connecte__n_a__accor_api_portfolio__api_portfolio__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__n_a__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_d_un_concept_de_corner_de_vente</t>
+          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__code_postal</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__ville__deja_dans_rod_au_moment_ou_le_user_se_connecte__n_a__accor_api_portfolio__api_portfolio__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__n_a__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_d_un_concept_de_corner_de_vente</t>
+          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__ville</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__longitude__deja_dans_rod_au_moment_ou_le_user_se_connecte__n_a__accor_api_portfolio__api_portfolio__bdd_accor_source__export_a_la_demande__le_user_peut_modifier_dans_rod__n_a__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_d_un_concept_de_corner_de_vente</t>
+          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__longitude</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__latitude__deja_dans_rod_au_moment_ou_le_user_se_connecte__n_a__accor_api_portfolio__api_portfolio__bdd_accor_source__export_a_la_demande__le_user_peut_modifier_dans_rod__n_a__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_d_un_concept_de_corner_de_vente</t>
+          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__latitude</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__marque__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__api_portfolio__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__non__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_fichier_parametres_regles_projections_nb_d_hotels</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__marque</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__nb_de_chambres__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__api_portfolio__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_fichier_parametres_regles_projections_nb_d_hotels</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__nb_de_chambres</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__contrat_signe_annee__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__tbc__bdd_accor_source____le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__n_a__commentaire_thomas_innolab__</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__contrat_signe_annee</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__contrat_type__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__tbc__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__n_a__commentaire_thomas_innolab__</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__contrat_type</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__proprietaire__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__tbc__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__n_a__commentaire_thomas_innolab__</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__proprietaire</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__dom_dof__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__tbc__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__n_a__commentaire_thomas_innolab__</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__dom_dof</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__pms__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__api_portfolio__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__n_a__commentaire_thomas_innolab__</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__derniere_reno_hotel</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__bar__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__tbc__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__derniere_reno_lobby</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__horaires_d_ouverture__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source____le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits__source_row__39</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__pms</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__jours_d_ouverture__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source____le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits__source_row__40</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_chiffrees__data__to_annuel</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__restaurant__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__tbc__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_chiffrees__data__to_le_plus_bas_taux</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__horaires_d_ouverture__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source____le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits__source_row__43</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_chiffrees__data__to_le_plus_haut_mois</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__jours_d_ouverture__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source____le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits__source_row__44</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_chiffrees__data__to_le_plus_haut_taux</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__mois_d_ouverture__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source____le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits__source_row__45</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__bar</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__non_f_b__data__salles_de_reunion__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__tbc__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__horaires_d_ouverture__source_row__39</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__non_f_b__data__salle_de_sport__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__tbc__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__jours_d_ouverture__source_row__40</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__non_f_b__data__piscine__deja_dans_rod_au_moment_ou_le_user_se_connecte__oui__accor_api_portfolio__tbc__bdd_accor_source__360_hotel_referential__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__restaurant</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__vitrine_refrigeree__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__si_l_hotel_possede_deja_une_vitrine_refrigeree_standard_et_que_le_corner_recommande_est_easy_ou_liberty_alors_le_nb_de_vitrine_a_acheter_est_a_0</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__horaires_d_ouverture__source_row__43</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__micro_ondes__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__jours_d_ouverture__source_row__44</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__fontaine_a_eau__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__mois_d_ouverture__source_row__45</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__machine_a_cafe__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__minibar</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__bouilloire__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__non_f_b__data__salles_de_reunion</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__loisirs__data__loisirs__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source____le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__non_f_b__data__salle_de_sport</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__loisirs__data__top_1_couples__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source____le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__non_f_b__data__piscine</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__loisirs__data__top_1_amis__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source____le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__vitrine_refrigeree</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__loisirs__data__top_1_familles__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source____le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__micro_ondes</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__affaires__data__affaires__deja_dans_rod_au_moment_ou_le_user_se_connecte__tbc__accor_api_portfolio__tbc__bdd_accor_source____le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_produits</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__fontaine_a_eau</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__boissons_alcoolisees__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__machine_a_cafe</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__produits_sales_frais__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__bouilloire</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__produits_sucres_frais__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__loisirs__data__loisirs</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__epicerie_fine__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__loisirs__data__top_1_couples</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__produits_cosmetiques__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__loisirs__data__top_1_amis</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__articles_pour_enfants__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__loisirs__data__top_1_familles</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__pret_a_porter__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__affaires__data__affaires</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__accessoires__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__national_vs_inter__data__national</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__souvenirs__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_3_dans_mes_3_simulateurs_excel_application_d_un_bonus_malus</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__national_vs_inter__data__international</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__corner_de_vente_actuel__data__votre_hotel_dispose_t_il_deja_d_un_corner_de_vente__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__ajouter_fonctionnalite_permettant_a_l_hotel_de_conserver_l_agencement_de_son_corner_existant</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__boissons_alcoolisees</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__liste_des_produits_f_b__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_pdts_vs_ce_que_l_hotel_vend_deja__source_row__85</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__produits_sales_frais</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__reception__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_d_une_solution_technologique_de_vente</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__produits_sucres_frais</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__snacking_comptoir__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_d_une_solution_technologique_de_vente</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__epicerie_fine</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__distributeur_auto__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_d_une_solution_technologique_de_vente</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__produits_cosmetiques</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__hotel_staff__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_du_mode_de_gestion</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__articles_pour_enfants</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__liste_des_produits_non_f_b__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_de_l_assortiment_pdts_vs_ce_que_l_hotel_vend_deja__source_row__99</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__pret_a_porter</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__reception__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_d_une_solution_technologique_de_vente</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__accessoires</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__distributeur_auto__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_d_une_solution_technologique_de_vente</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__souvenirs</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__hotel_staff__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__non__commentaire_thomas_innolab__pourrait_etre_utilise_par_l_ia_pour_affiner_la_recommandation_du_mode_de_gestion</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__corner_de_vente_actuel__data__votre_hotel_dispose_t_il_deja_d_un_corner_de_vente</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__corner_de_vente_actuel__data__metres_lineaires_estimation__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__voir_regle_n_4_dans_mes_3_simulateurs_excel</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__liste_des_produits_f_b__source_row__85</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__corner_de_vente_actuel__data__metres_carres_estimation__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__oui__commentaire_thomas_innolab__</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__reception</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__wifi__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__n_a__commentaire_thomas_innolab____source_row__122</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__snacking_comptoir</t>
         </is>
       </c>
       <c r="BH1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__internet_filaire_prise_rj45__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__n_a__commentaire_thomas_innolab____source_row__123</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__distributeur_auto</t>
         </is>
       </c>
       <c r="BI1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__alimentation_electrique__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__n_a__commentaire_thomas_innolab____source_row__124</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__hotel_staff</t>
         </is>
       </c>
       <c r="BJ1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__videosurveillance__deja_dans_rod_au_moment_ou_le_user_se_connecte__non__accor_api_portfolio__non__bdd_accor_source__n_a__le_user_peut_modifier_dans_rod__oui__data_exploitee_dans_la_simulation_actuellement__n_a__commentaire_thomas_innolab____source_row__125</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__liste_des_produits_non_f_b__source_row__99</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__reception</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__distributeur_auto</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__hotel_staff</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__corner_de_vente_actuel__data__metres_lineaires_estimation</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__corner_de_vente_actuel__data__metres_carres_estimation</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__wifi__source_row__122</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__internet_filaire_prise_rj45__source_row__123</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__alimentation_electrique__source_row__124</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__videosurveillance__source_row__125</t>
         </is>
       </c>
     </row>
@@ -809,59 +854,49 @@
           <t>Marion BOROT</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
         <is>
           <t>FOLS</t>
         </is>
       </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="inlineStr">
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
         <v>4</v>
       </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
       <c r="AH2" t="n">
         <v>0</v>
       </c>
@@ -869,82 +904,103 @@
         <v>1</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1</v>
+      </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
         <v>1</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC2" t="n">
         <v>1</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN2" t="n">
         <v>3</v>
       </c>
-      <c r="BF2" t="n">
+      <c r="BO2" t="n">
         <v>6</v>
       </c>
-      <c r="BG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ2" t="n">
+      <c r="BP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1019,60 +1075,62 @@
           <t>Christophe RUQUEBOEUCHE</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>OPERA</t>
         </is>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>DECEMBRE</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>16h - 00h</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>MARDI AU SAMEDI</t>
         </is>
       </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="inlineStr">
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1</v>
-      </c>
       <c r="AE3" t="n">
         <v>1</v>
       </c>
@@ -1080,49 +1138,49 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
         <v>0.6</v>
       </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
         <v>0.4</v>
       </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
         <v>1</v>
@@ -1131,42 +1189,69 @@
         <v>1</v>
       </c>
       <c r="AX3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
         <v>1</v>
       </c>
       <c r="BE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN3" t="n">
         <v>2</v>
       </c>
-      <c r="BF3" t="n">
+      <c r="BO3" t="n">
         <v>2</v>
       </c>
-      <c r="BG3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BJ3" t="n">
+      <c r="BP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1241,107 +1326,109 @@
           <t>Sophie CHOLLON</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" t="n">
+        <v>2015</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2015</v>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>FOLS</t>
         </is>
       </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>AOUT</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>07h-23h</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>TOUS</t>
         </is>
       </c>
-      <c r="U4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" t="inlineStr">
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>18h-22h</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>TOUS</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>TOUS</t>
         </is>
       </c>
-      <c r="Y4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1</v>
-      </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
         <v>1</v>
       </c>
       <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="n">
         <v>80</v>
       </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK4" t="n">
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="n">
         <v>20</v>
       </c>
-      <c r="AL4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="AU4" t="n">
         <v>1</v>
@@ -1353,19 +1440,19 @@
         <v>1</v>
       </c>
       <c r="AX4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
         <v>1</v>
@@ -1373,18 +1460,45 @@
       <c r="BD4" t="n">
         <v>1</v>
       </c>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
+      <c r="BE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1</v>
+      </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN4" t="inlineStr"/>
+      <c r="BO4" t="inlineStr"/>
+      <c r="BP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1457,98 +1571,82 @@
           <t>Bello DIALLO</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
         <is>
           <t>FOLS</t>
         </is>
       </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="n">
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
         <v>3</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AG5" t="n">
         <v>2</v>
       </c>
-      <c r="AA5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
       <c r="AL5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
         <v>1</v>
       </c>
-      <c r="AR5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1</v>
-      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ5" t="n">
         <v>1</v>
@@ -1560,13 +1658,17 @@
         <v>1</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1</v>
+      </c>
       <c r="BG5" t="n">
         <v>0</v>
       </c>
@@ -1574,9 +1676,32 @@
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN5" t="inlineStr"/>
+      <c r="BO5" t="inlineStr"/>
+      <c r="BP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1651,126 +1776,137 @@
           <t>Philippe JAUSSELY</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
         <is>
           <t>OPERA</t>
         </is>
       </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="n">
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
         <v>36</v>
       </c>
-      <c r="Z6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="inlineStr"/>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1</v>
+      </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
         <v>1</v>
       </c>
-      <c r="AR6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1</v>
-      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
         <v>1</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY6" t="n">
         <v>1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC6" t="n">
         <v>1</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
       <c r="BG6" t="n">
         <v>0</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BI6" t="n">
         <v>0</v>
       </c>
       <c r="BJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1843,84 +1979,68 @@
           <t>Thibault FREMONT</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
         <is>
           <t>OPERA</t>
         </is>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1</v>
-      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="n">
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1</v>
+      </c>
       <c r="AH7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
-      <c r="AK7" t="inlineStr"/>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
       <c r="AL7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
         <v>1</v>
       </c>
       <c r="AP7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
       <c r="AU7" t="n">
         <v>1</v>
       </c>
@@ -1931,10 +2051,10 @@
         <v>1</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ7" t="n">
         <v>1</v>
@@ -1946,13 +2066,17 @@
         <v>1</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD7" t="n">
         <v>1</v>
       </c>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
+      <c r="BE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1</v>
+      </c>
       <c r="BG7" t="n">
         <v>0</v>
       </c>
@@ -1960,9 +2084,32 @@
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN7" t="inlineStr"/>
+      <c r="BO7" t="inlineStr"/>
+      <c r="BP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2035,68 +2182,58 @@
           <t>Hubert VANQUATHEM</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
         <is>
           <t>OPERA</t>
         </is>
       </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
-      <c r="U8" t="n">
-        <v>2</v>
-      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="n">
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
         <v>13</v>
       </c>
-      <c r="Z8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="inlineStr"/>
+      <c r="AG8" t="n">
+        <v>1</v>
+      </c>
       <c r="AH8" t="n">
         <v>1</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
-      <c r="AK8" t="inlineStr"/>
+      <c r="AK8" t="n">
+        <v>1</v>
+      </c>
       <c r="AL8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP8" t="n">
         <v>0</v>
@@ -2104,15 +2241,9 @@
       <c r="AQ8" t="n">
         <v>0</v>
       </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
       <c r="AU8" t="n">
         <v>1</v>
       </c>
@@ -2129,7 +2260,7 @@
         <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
         <v>0</v>
@@ -2143,8 +2274,12 @@
       <c r="BD8" t="n">
         <v>1</v>
       </c>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
+      <c r="BE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1</v>
+      </c>
       <c r="BG8" t="n">
         <v>0</v>
       </c>
@@ -2152,9 +2287,32 @@
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN8" t="inlineStr"/>
+      <c r="BO8" t="inlineStr"/>
+      <c r="BP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
         <v>0</v>
       </c>
     </row>
